--- a/data/trans_orig/Q20A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q20A-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que ha estado hospitalizado en los últimos 12 meses</t>
+          <t>Número medio de veces que la población ha estado hospitalizada en los últimos 12 meses (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -751,7 +751,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,13</t>
+          <t>0,04; 0,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,09</t>
+          <t>0,04; 0,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,08</t>
+          <t>0,02; 0,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,4</t>
+          <t>0,02; 0,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,16</t>
+          <t>0,1; 0,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,22</t>
+          <t>0,13; 0,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,13</t>
+          <t>0,09; 0,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,24</t>
+          <t>0,05; 0,19</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,11</t>
+          <t>0,05; 0,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,07</t>
+          <t>0,03; 0,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,09</t>
+          <t>0,04; 0,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1026,27 +1026,27 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>0,07; 0,13</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0,06; 0,1</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0,03; 0,06</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>0,07; 0,12</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,11</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>0,03; 0,06</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 0,12</t>
-        </is>
-      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,09</t>
+          <t>0,05; 0,08</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0,04; 0,12</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0,05; 0,12</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0,03; 0,17</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0,03; 0,19</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,04; 0,09</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,06; 0,12</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0,04; 0,1</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0,04; 0,09</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0,04; 0,1</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0,06; 0,11</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0,05; 0,12</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>0,04; 0,13</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,05; 0,13</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,03; 0,17</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,03; 0,18</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,04; 0,09</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,12</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0,04; 0,1</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0,04; 0,09</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0,04; 0,09</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,11</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>0,04; 0,11</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,04; 0,12</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,2</t>
+          <t>0,05; 0,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,23</t>
+          <t>0,07; 0,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1311,17 +1311,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,09</t>
+          <t>0,05; 0,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,15</t>
+          <t>0,06; 0,14</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,16</t>
+          <t>0,07; 0,15</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,18</t>
+          <t>0,07; 0,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,14</t>
+          <t>0,08; 0,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,31</t>
+          <t>0,1; 0,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,24</t>
+          <t>0,11; 0,22</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,15</t>
+          <t>0,09; 0,15</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,1</t>
+          <t>0,03; 0,09</t>
         </is>
       </c>
     </row>
@@ -1556,27 +1556,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,31</t>
+          <t>0,11; 0,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,19</t>
+          <t>0,16; 1,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,2</t>
+          <t>0,09; 0,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,19</t>
+          <t>0,11; 0,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,37</t>
+          <t>0,11; 0,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,25</t>
+          <t>0,1; 0,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1596,17 +1596,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,31</t>
+          <t>0,13; 0,3</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,51</t>
+          <t>0,16; 0,53</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,2</t>
+          <t>0,11; 0,2</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1701,27 +1701,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,13</t>
+          <t>0,07; 0,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,08</t>
+          <t>0,05; 0,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,11</t>
+          <t>0,06; 0,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,12</t>
+          <t>0,08; 0,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,13</t>
+          <t>0,1; 0,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">

--- a/data/trans_orig/Q20A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q20A-Edad-trans_orig.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>0,04</t>
         </is>
       </c>
     </row>
@@ -736,12 +736,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,09</t>
+          <t>0,04; 0,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,11</t>
+          <t>0,05; 0,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,12</t>
+          <t>0,05; 0,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,09</t>
+          <t>0,05; 0,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,06</t>
+          <t>0,02; 0,08</t>
         </is>
       </c>
     </row>
@@ -803,47 +803,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>0,11</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,12</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,17</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0,12</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0,09</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0,08</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>0,1</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>0,07</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,1</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,07</t>
+          <t>0,03; 0,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,38</t>
+          <t>0,02; 0,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,15</t>
+          <t>0,1; 0,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,1</t>
+          <t>0,06; 0,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,13</t>
+          <t>0,08; 0,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,19</t>
+          <t>0,06; 0,26</t>
         </is>
       </c>
     </row>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,08</t>
+          <t>0,03; 0,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,08</t>
+          <t>0,04; 0,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,13</t>
+          <t>0,07; 0,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,06</t>
+          <t>0,04; 0,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,12</t>
+          <t>0,07; 0,11</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1083,47 +1083,47 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>0,11</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,06</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,09</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0,07</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0,06</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0,06</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0,08</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>0,06</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,08</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,12</t>
+          <t>0,04; 0,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,19</t>
+          <t>0,06; 0,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,12</t>
+          <t>0,05; 0,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,13</t>
+          <t>0,06; 0,17</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,14</t>
+          <t>0,08; 0,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1301,12 +1301,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,22</t>
+          <t>0,07; 0,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,11</t>
+          <t>0,04; 0,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,15</t>
+          <t>0,07; 0,16</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,09</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,19</t>
+          <t>0,08; 0,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,18</t>
+          <t>0,07; 0,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,2</t>
+          <t>0,09; 0,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>0,08; 0,14</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,1; 0,34</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>0,08; 0,15</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 0,31</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0,06; 0,13</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0,06; 0,12</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0,11; 0,23</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0,09; 0,15</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>0,08; 0,15</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,14</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0,02; 0,08</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>0,11; 0,22</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>0,09; 0,15</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>0,09; 0,15</t>
-        </is>
-      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,09</t>
+          <t>0,07; 0,11</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1556,27 +1556,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,32</t>
+          <t>0,11; 0,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,01</t>
+          <t>0,16; 1,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,2</t>
+          <t>0,08; 0,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,19</t>
+          <t>0,1; 0,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,37</t>
+          <t>0,12; 0,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,16</t>
+          <t>0,1; 0,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,53</t>
+          <t>0,17; 0,48</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,2</t>
+          <t>0,11; 0,21</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1643,27 +1643,27 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>0,09</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,12</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0,09</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>0,08</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1706,17 +1706,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,09</t>
+          <t>0,05; 0,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,12</t>
+          <t>0,07; 0,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,12</t>
+          <t>0,09; 0,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,08</t>
+          <t>0,07; 0,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,09</t>
+          <t>0,07; 0,1</t>
         </is>
       </c>
     </row>
